--- a/outputs/59639.xlsx
+++ b/outputs/59639.xlsx
@@ -138,12 +138,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,141 +344,141 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="0" t="str">
+      <c r="D5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>A</v>
       </c>
-      <c r="E5" s="0" t="str">
+      <c r="E5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>B</v>
       </c>
-      <c r="F5" s="0" t="str">
+      <c r="F5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>C</v>
       </c>
-      <c r="G5" s="0" t="str">
+      <c r="G5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>D</v>
       </c>
-      <c r="H5" s="0" t="str">
+      <c r="H5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>E</v>
       </c>
-      <c r="I5" s="0" t="str">
+      <c r="I5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>F</v>
       </c>
-      <c r="J5" s="0" t="str">
+      <c r="J5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>G</v>
       </c>
-      <c r="K5" s="0" t="str">
+      <c r="K5" s="1" t="str">
         <f aca="false">MID($A5,COLUMN()-3,1)</f>
         <v>H</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="0" t="str">
+      <c r="D6" s="1" t="str">
         <f aca="false">MID($A6,COLUMN()-3,1)</f>
         <v>p</v>
       </c>
-      <c r="E6" s="0" t="str">
+      <c r="E6" s="1" t="str">
         <f aca="false">MID($A6,COLUMN()-3,1)</f>
         <v>q</v>
       </c>
-      <c r="F6" s="0" t="str">
+      <c r="F6" s="1" t="str">
         <f aca="false">MID($A6,COLUMN()-3,1)</f>
         <v>r</v>
       </c>
-      <c r="G6" s="0" t="str">
+      <c r="G6" s="1" t="str">
         <f aca="false">MID($A6,COLUMN()-3,1)</f>
         <v>s</v>
       </c>
-      <c r="H6" s="0" t="str">
+      <c r="H6" s="1" t="str">
         <f aca="false">MID($A6,COLUMN()-3,1)</f>
         <v>t</v>
       </c>
-      <c r="I6" s="0" t="str">
-        <f aca="false">MID($A6,COLUMN()-3,1)</f>
-        <v/>
-      </c>
-      <c r="J6" s="0" t="str">
-        <f aca="false">MID($A6,COLUMN()-3,1)</f>
-        <v/>
-      </c>
-      <c r="K6" s="0" t="str">
+      <c r="I6" s="1" t="str">
+        <f aca="false">MID($A6,COLUMN()-3,1)</f>
+        <v/>
+      </c>
+      <c r="J6" s="1" t="str">
+        <f aca="false">MID($A6,COLUMN()-3,1)</f>
+        <v/>
+      </c>
+      <c r="K6" s="1" t="str">
         <f aca="false">MID($A6,COLUMN()-3,1)</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="0" t="str">
+      <c r="D7" s="1" t="str">
         <f aca="false">MID($A7,COLUMN()-3,1)</f>
         <v>x</v>
       </c>
-      <c r="E7" s="0" t="str">
+      <c r="E7" s="1" t="str">
         <f aca="false">MID($A7,COLUMN()-3,1)</f>
         <v>y</v>
       </c>
-      <c r="F7" s="0" t="str">
+      <c r="F7" s="1" t="str">
         <f aca="false">MID($A7,COLUMN()-3,1)</f>
         <v>z</v>
       </c>
-      <c r="G7" s="0" t="str">
-        <f aca="false">MID($A7,COLUMN()-3,1)</f>
-        <v/>
-      </c>
-      <c r="H7" s="0" t="str">
-        <f aca="false">MID($A7,COLUMN()-3,1)</f>
-        <v/>
-      </c>
-      <c r="I7" s="0" t="str">
-        <f aca="false">MID($A7,COLUMN()-3,1)</f>
-        <v/>
-      </c>
-      <c r="J7" s="0" t="str">
-        <f aca="false">MID($A7,COLUMN()-3,1)</f>
-        <v/>
-      </c>
-      <c r="K7" s="0" t="str">
+      <c r="G7" s="1" t="str">
+        <f aca="false">MID($A7,COLUMN()-3,1)</f>
+        <v/>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f aca="false">MID($A7,COLUMN()-3,1)</f>
+        <v/>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f aca="false">MID($A7,COLUMN()-3,1)</f>
+        <v/>
+      </c>
+      <c r="J7" s="1" t="str">
+        <f aca="false">MID($A7,COLUMN()-3,1)</f>
+        <v/>
+      </c>
+      <c r="K7" s="1" t="str">
         <f aca="false">MID($A7,COLUMN()-3,1)</f>
         <v/>
       </c>
